--- a/ig/ch-core/StructureDefinition-ch-core-address-ech-11-placeofbirth.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-address-ech-11-placeofbirth.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="337">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,7 +658,7 @@
     <t>streetName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.3.0}
 </t>
   </si>
   <si>
@@ -680,7 +680,7 @@
     <t>houseNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.3.0}
 </t>
   </si>
   <si>
@@ -702,7 +702,7 @@
     <t>unitID</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-unitID|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {iso21090-ADXP-unitID|5.3.0}
 </t>
   </si>
   <si>
@@ -751,7 +751,7 @@
     <t>postOfficeBoxNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-postBox|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {iso21090-ADXP-postBox|5.3.0}
 </t>
   </si>
   <si>
@@ -943,6 +943,12 @@
     <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://fhir.ch/ig/ch-term/ValueSet/bfs-country-codes</t>
+  </si>
+  <si>
     <t>BFS-322</t>
   </si>
   <si>
@@ -973,14 +979,14 @@
     <t>countrycode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-codedString|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {iso21090-codedString|5.3.0}
 </t>
   </si>
   <si>
     <t>ISO Country Alpha-2 or ISO Country Alpha-3 code</t>
   </si>
   <si>
-    <t>The content of the country code element (if present) SHALL be selected EITHER from ValueSet ISO Country Alpha-2 http://hl7.org/fhir/ValueSet/iso3166-1-2 OR MAY be selected from ISO Country Alpha-3 Value Set http://hl7.org/fhir/ValueSet/iso3166-1-3, if the country is not specified in value Set ISO Country Alpha-2 http://hl7.org/fhir/ValueSet/iso3166-1-2.</t>
+    <t>BFS defines the valid set of countries. Values are from the 'ISO 3166-1 country codes' code system.</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -988,6 +994,37 @@
   </si>
   <si>
     <t>SC.code</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countrycode.id</t>
+  </si>
+  <si>
+    <t>Address.country.extension.id</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countrycode.extension</t>
+  </si>
+  <si>
+    <t>Address.country.extension.extension</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countrycode.url</t>
+  </si>
+  <si>
+    <t>Address.country.extension.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/iso21090-codedString</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countrycode.value[x]</t>
+  </si>
+  <si>
+    <t>Address.country.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
   </si>
   <si>
     <t>Address.country.value</t>
@@ -1333,11 +1370,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP53"/>
+  <dimension ref="A1:AP57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.51953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.93359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.10546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.18359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -7036,13 +7073,11 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7075,30 +7110,30 @@
         <v>123</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7213,10 +7248,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7329,13 +7364,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
@@ -7357,13 +7392,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7426,7 +7461,7 @@
         <v>88</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
@@ -7438,7 +7473,7 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -7449,10 +7484,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7478,10 +7513,10 @@
         <v>96</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>244</v>
+        <v>97</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>245</v>
+        <v>98</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7505,7 +7540,7 @@
         <v>81</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
         <v>81</v>
@@ -7532,7 +7567,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>247</v>
+        <v>99</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -7556,7 +7591,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -7567,10 +7602,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7590,21 +7625,19 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>317</v>
+        <v>103</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>318</v>
+        <v>157</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>319</v>
+        <v>158</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -7616,72 +7649,546 @@
         <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="U53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
+      <c r="B54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y55" s="2"/>
+      <c r="Z55" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="AK53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AP53" t="s" s="2">
+      <c r="AK55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>81</v>
       </c>
     </row>
